--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_4_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_4_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902649F2-F270-4B6B-992C-CCAFEE689024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5685F7E2-1810-442B-A4F7-BD162DD21E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,40 +55,52 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT HINDPETRO 29 May 2025 410 PE</t>
-  </si>
-  <si>
-    <t>05-05-2025</t>
-  </si>
-  <si>
-    <t>OPT SBILIFE 29 May 2025 1740 PE</t>
-  </si>
-  <si>
-    <t>06-05-2025</t>
-  </si>
-  <si>
-    <t>OPT SBIN 29 May 2025 780 PE</t>
-  </si>
-  <si>
-    <t>OPT TATAMOTORS 29 May 2025 660 PE</t>
-  </si>
-  <si>
-    <t>07-05-2025</t>
-  </si>
-  <si>
-    <t>OPT TATAMOTORS 29 May 2025 660 CE</t>
-  </si>
-  <si>
-    <t>OPT PATANJALI 29 May 2025 1800 PE</t>
-  </si>
-  <si>
-    <t>OPT APOLLOTYRE 29 May 2025 460 PE</t>
-  </si>
-  <si>
-    <t>09-05-2025</t>
-  </si>
-  <si>
-    <t>OPT BHARATFORG 29 May 2025 1140 CE</t>
+    <t>OPT NIFTY 05 Jun 2025 24600 CE</t>
+  </si>
+  <si>
+    <t>02-06-2025</t>
+  </si>
+  <si>
+    <t>OPT APOLLOHOSP 26 Jun 2025 7000 CE</t>
+  </si>
+  <si>
+    <t>OPT MPHASIS 26 Jun 2025 2460 PE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 05 Jun 2025 24600 PE</t>
+  </si>
+  <si>
+    <t>03-06-2025</t>
+  </si>
+  <si>
+    <t>OPT ADANIPORTS 26 Jun 2025 1440 CE</t>
+  </si>
+  <si>
+    <t>OPT POLICYBZR 26 Jun 2025 1780 CE</t>
+  </si>
+  <si>
+    <t>04-06-2025</t>
+  </si>
+  <si>
+    <t>OPT DRREDDY 26 Jun 2025 1290 CE</t>
+  </si>
+  <si>
+    <t>05-06-2025</t>
+  </si>
+  <si>
+    <t>OPT LAURUSLABS 26 Jun 2025 640 CE</t>
+  </si>
+  <si>
+    <t>OPT GLENMARK 26 Jun 2025 1560 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 12 Jun 2025 24900 CE</t>
+  </si>
+  <si>
+    <t>06-06-2025</t>
+  </si>
+  <si>
+    <t>OPT DLF 26 Jun 2025 830 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -441,10 +453,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -460,10 +472,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -472,10 +484,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -498,378 +510,566 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45782</v>
+        <v>45810</v>
       </c>
       <c r="D2">
-        <v>2025</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>16.8</v>
+        <v>230.5</v>
       </c>
       <c r="F2">
-        <v>34020</v>
+        <v>17287.5</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>2025</v>
+        <v>75</v>
       </c>
       <c r="I2">
-        <v>16.5</v>
+        <v>236.65</v>
       </c>
       <c r="J2">
-        <v>33412.5</v>
+        <v>17748.75</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>-607.5</v>
+        <v>461.25</v>
       </c>
       <c r="M2">
-        <v>109.56</v>
+        <v>80.2</v>
       </c>
       <c r="N2">
-        <v>-717.06</v>
+        <v>381.05</v>
       </c>
       <c r="O2">
-        <v>607.5</v>
+        <v>461.25</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>248</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45783</v>
+        <v>45810</v>
       </c>
       <c r="D3">
-        <v>375</v>
+        <v>125</v>
       </c>
       <c r="E3">
-        <v>47.5</v>
+        <v>235.95</v>
       </c>
       <c r="F3">
-        <v>17812.5</v>
+        <v>29493.75</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>375</v>
+        <v>125</v>
       </c>
       <c r="I3">
-        <v>48.3</v>
+        <v>232.55</v>
       </c>
       <c r="J3">
-        <v>18112.5</v>
+        <v>29068.75</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>300</v>
+        <v>-425</v>
       </c>
       <c r="M3">
-        <v>80.94</v>
+        <v>101.96</v>
       </c>
       <c r="N3">
-        <v>219.06</v>
+        <v>-526.96</v>
       </c>
       <c r="O3">
-        <v>300</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>249</v>
+        <v>179</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>45783</v>
+        <v>45810</v>
       </c>
       <c r="D4">
-        <v>750</v>
+        <v>275</v>
       </c>
       <c r="E4">
-        <v>27.9</v>
+        <v>81.05</v>
       </c>
       <c r="F4">
-        <v>20925</v>
+        <v>22288.75</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>750</v>
+        <v>275</v>
       </c>
       <c r="I4">
-        <v>29.35</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="J4">
-        <v>22012.5</v>
+        <v>20927.5</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1087.5</v>
+        <v>-1361.25</v>
       </c>
       <c r="M4">
-        <v>87.61</v>
+        <v>86.97</v>
       </c>
       <c r="N4">
-        <v>999.89</v>
+        <v>-1448.22</v>
       </c>
       <c r="O4">
-        <v>1087.5</v>
+        <v>1361.25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>267</v>
+        <v>190</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45811</v>
+      </c>
+      <c r="D5">
+        <v>75</v>
+      </c>
+      <c r="E5">
+        <v>172.9</v>
+      </c>
+      <c r="F5">
+        <v>12967.5</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1">
-        <v>45784</v>
-      </c>
-      <c r="D5">
-        <v>550</v>
-      </c>
-      <c r="E5">
-        <v>22.65</v>
-      </c>
-      <c r="F5">
-        <v>12457.5</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="H5">
-        <v>550</v>
+        <v>75</v>
       </c>
       <c r="I5">
-        <v>21.7</v>
+        <v>141.75</v>
       </c>
       <c r="J5">
-        <v>11935</v>
+        <v>10631.25</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-522.5</v>
+        <v>-2336.25</v>
       </c>
       <c r="M5">
-        <v>69.77</v>
+        <v>68.14</v>
       </c>
       <c r="N5">
-        <v>-592.27</v>
+        <v>-2404.39</v>
       </c>
       <c r="O5">
-        <v>522.5</v>
+        <v>2336.25</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
-        <v>45784</v>
+        <v>45811</v>
       </c>
       <c r="D6">
-        <v>550</v>
+        <v>75</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>255.6</v>
       </c>
       <c r="F6">
-        <v>20900</v>
+        <v>19170</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>550</v>
+        <v>75</v>
       </c>
       <c r="I6">
-        <v>33.5</v>
+        <v>268.89999999999998</v>
       </c>
       <c r="J6">
-        <v>18425</v>
+        <v>20167.5</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>-2475</v>
+        <v>997.5</v>
       </c>
       <c r="M6">
-        <v>82.89</v>
+        <v>84.38</v>
       </c>
       <c r="N6">
-        <v>-2557.89</v>
+        <v>913.12</v>
       </c>
       <c r="O6">
-        <v>2475</v>
+        <v>997.5</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>45784</v>
+        <v>45811</v>
       </c>
       <c r="D7">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E7">
-        <v>57.95</v>
+        <v>47.33</v>
       </c>
       <c r="F7">
-        <v>17385</v>
+        <v>37860</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="I7">
-        <v>50.05</v>
+        <v>46.5</v>
       </c>
       <c r="J7">
-        <v>15015</v>
+        <v>37200</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>-2370</v>
+        <v>-660</v>
       </c>
       <c r="M7">
-        <v>76.36</v>
+        <v>164.3</v>
       </c>
       <c r="N7">
-        <v>-2446.36</v>
+        <v>-824.3</v>
       </c>
       <c r="O7">
-        <v>2370</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>235</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
       <c r="C8" s="1">
-        <v>45786</v>
+        <v>45812</v>
       </c>
       <c r="D8">
-        <v>1700</v>
+        <v>325</v>
       </c>
       <c r="E8">
-        <v>15.3</v>
+        <v>73</v>
       </c>
       <c r="F8">
-        <v>26010</v>
+        <v>23725</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>1700</v>
+        <v>325</v>
       </c>
       <c r="I8">
-        <v>15.45</v>
+        <v>66</v>
       </c>
       <c r="J8">
-        <v>26265</v>
+        <v>21450</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>255</v>
+        <v>-2275</v>
       </c>
       <c r="M8">
-        <v>96.23</v>
+        <v>88.2</v>
       </c>
       <c r="N8">
-        <v>158.77000000000001</v>
+        <v>-2363.1999999999998</v>
       </c>
       <c r="O8">
-        <v>255</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1">
-        <v>45786</v>
+        <v>45813</v>
       </c>
       <c r="D9">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="E9">
-        <v>54.15</v>
+        <v>30.15</v>
       </c>
       <c r="F9">
-        <v>27075</v>
+        <v>18843.75</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H9">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="I9">
-        <v>55</v>
+        <v>30.8</v>
       </c>
       <c r="J9">
-        <v>27500</v>
+        <v>19250</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>425</v>
+        <v>406.25</v>
       </c>
       <c r="M9">
-        <v>99.09</v>
+        <v>83.04</v>
       </c>
       <c r="N9">
-        <v>325.91000000000003</v>
+        <v>323.20999999999998</v>
       </c>
       <c r="O9">
-        <v>425</v>
+        <v>406.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>160</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45813</v>
+      </c>
+      <c r="D10">
+        <v>1700</v>
+      </c>
+      <c r="E10">
+        <v>23.05</v>
+      </c>
+      <c r="F10">
+        <v>39185</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10">
+        <v>1700</v>
+      </c>
+      <c r="I10">
+        <v>23.75</v>
+      </c>
+      <c r="J10">
+        <v>40375</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1190</v>
+      </c>
+      <c r="M10">
+        <v>121.67</v>
+      </c>
+      <c r="N10">
+        <v>1068.33</v>
+      </c>
+      <c r="O10">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45813</v>
+      </c>
+      <c r="D11">
+        <v>325</v>
+      </c>
+      <c r="E11">
+        <v>56.6</v>
+      </c>
+      <c r="F11">
+        <v>18395</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11">
+        <v>325</v>
+      </c>
+      <c r="I11">
+        <v>57.25</v>
+      </c>
+      <c r="J11">
+        <v>18606.25</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>211.25</v>
+      </c>
+      <c r="M11">
+        <v>81.92</v>
+      </c>
+      <c r="N11">
+        <v>129.33000000000001</v>
+      </c>
+      <c r="O11">
+        <v>211.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>201</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45814</v>
+      </c>
+      <c r="D12">
+        <v>75</v>
+      </c>
+      <c r="E12">
+        <v>237.65</v>
+      </c>
+      <c r="F12">
+        <v>17823.75</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>75</v>
+      </c>
+      <c r="I12">
+        <v>248.75</v>
+      </c>
+      <c r="J12">
+        <v>18656.25</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>832.5</v>
+      </c>
+      <c r="M12">
+        <v>81.73</v>
+      </c>
+      <c r="N12">
+        <v>750.77</v>
+      </c>
+      <c r="O12">
+        <v>832.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>92</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45814</v>
+      </c>
+      <c r="D13">
+        <v>825</v>
+      </c>
+      <c r="E13">
+        <v>24.95</v>
+      </c>
+      <c r="F13">
+        <v>20583.75</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>825</v>
+      </c>
+      <c r="I13">
+        <v>24.15</v>
+      </c>
+      <c r="J13">
+        <v>19923.75</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>-660</v>
+      </c>
+      <c r="M13">
+        <v>85.04</v>
+      </c>
+      <c r="N13">
+        <v>-745.04</v>
+      </c>
+      <c r="O13">
+        <v>660</v>
       </c>
     </row>
   </sheetData>
